--- a/data/ams_weekly_data/Fossil/business_report_week31.xlsx
+++ b/data/ams_weekly_data/Fossil/business_report_week31.xlsx
@@ -1400,7 +1400,7 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -1412,7 +1412,7 @@
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>368488.98</v>
+        <v>356205.93</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
